--- a/data/monthly/【2025年12月】月次数値.xlsx
+++ b/data/monthly/【2025年12月】月次数値.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="612" yWindow="600" windowWidth="21792" windowHeight="10812"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="121">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -254,31 +253,159 @@
   </si>
   <si>
     <t>MOMO DENTAL CLINIC（リンクURL変更前）</t>
+  </si>
+  <si>
+    <t>有限会社 ムネケン</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>堀田歯科（リンク先変更前）</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>堀田歯科</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>archived</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>竹内歯科クリニック（審美歯科）</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>大神宮デンタルクリニック</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>千歳烏山ケンズ歯科</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>整体処 たくみ堂</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>住友歯科医院</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>むぎ歯科</t>
+  </si>
+  <si>
+    <t>はんだ歯科医院</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>はま歯科医院</t>
+  </si>
+  <si>
+    <t>なかはら歯科クリニック</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>ストレッチ&amp;ボディケア m.o.v.e巣鴨店</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>すがや歯科クリニック</t>
+  </si>
+  <si>
+    <t>2026-11-03</t>
+  </si>
+  <si>
+    <t>スカイハイ英語塾</t>
+  </si>
+  <si>
+    <t>きしかわデンタルオフィス</t>
+  </si>
+  <si>
+    <t>2026-11-27</t>
+  </si>
+  <si>
+    <t>UESUGI美容鍼灸整骨院</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>Sheena HEALING SALON</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>PML　広尾店</t>
+  </si>
+  <si>
+    <t>GAJUM photo studio</t>
+  </si>
+  <si>
+    <t>DesignBody 御徒町店</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>COCORO エステサロン</t>
+  </si>
+  <si>
+    <t>Beauty Salon Arona</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -286,36 +413,36 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -604,14 +731,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:Y30"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="20" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Y57"/>
+  <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -688,7 +812,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -738,7 +862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -788,7 +912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -838,7 +962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -864,10 +988,10 @@
         <v>2630</v>
       </c>
       <c r="I5">
-        <v>1.393156</v>
+        <v>1.3931560000000001</v>
       </c>
       <c r="J5">
-        <v>71.53623188</v>
+        <v>71.536231880000003</v>
       </c>
       <c r="K5">
         <v>320</v>
@@ -891,16 +1015,16 @@
         <v>69</v>
       </c>
       <c r="S5">
-        <v>71.536232</v>
+        <v>71.536231999999998</v>
       </c>
       <c r="T5">
-        <v>1.883188</v>
+        <v>1.8831880000000001</v>
       </c>
       <c r="U5">
         <v>75</v>
       </c>
       <c r="V5">
-        <v>2.046943</v>
+        <v>2.0469430000000002</v>
       </c>
       <c r="W5">
         <v>65.813333</v>
@@ -912,7 +1036,7 @@
         <v>197.44</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -938,10 +1062,10 @@
         <v>2184</v>
       </c>
       <c r="I6">
-        <v>1.324634</v>
+        <v>1.3246340000000001</v>
       </c>
       <c r="J6">
-        <v>58.02352941</v>
+        <v>58.023529410000002</v>
       </c>
       <c r="K6">
         <v>160</v>
@@ -965,28 +1089,28 @@
         <v>85</v>
       </c>
       <c r="S6">
-        <v>58.023529</v>
+        <v>58.023529000000003</v>
       </c>
       <c r="T6">
-        <v>2.938127</v>
+        <v>2.9381270000000002</v>
       </c>
       <c r="U6">
         <v>89</v>
       </c>
       <c r="V6">
-        <v>3.076391</v>
+        <v>3.0763910000000001</v>
       </c>
       <c r="W6">
-        <v>55.41573</v>
+        <v>55.415730000000003</v>
       </c>
       <c r="X6">
         <v>62</v>
       </c>
       <c r="Y6">
-        <v>79.548387</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25">
+        <v>79.548387000000005</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1012,10 +1136,10 @@
         <v>2175</v>
       </c>
       <c r="I7">
-        <v>1.357241</v>
+        <v>1.3572409999999999</v>
       </c>
       <c r="J7">
-        <v>62.11392405</v>
+        <v>62.113924050000001</v>
       </c>
       <c r="K7">
         <v>160</v>
@@ -1033,34 +1157,34 @@
         <v>2952</v>
       </c>
       <c r="P7">
-        <v>1662.262873</v>
+        <v>1662.2628729999999</v>
       </c>
       <c r="Q7">
         <v>79</v>
       </c>
       <c r="S7">
-        <v>62.113924</v>
+        <v>62.113923999999997</v>
       </c>
       <c r="T7">
-        <v>2.676152</v>
+        <v>2.6761520000000001</v>
       </c>
       <c r="U7">
         <v>83</v>
       </c>
       <c r="V7">
-        <v>2.811653</v>
+        <v>2.8116530000000002</v>
       </c>
       <c r="W7">
-        <v>59.120482</v>
+        <v>59.120482000000003</v>
       </c>
       <c r="X7">
         <v>59</v>
       </c>
       <c r="Y7">
-        <v>83.169492</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25">
+        <v>83.169492000000005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1089,7 +1213,7 @@
         <v>1.366306</v>
       </c>
       <c r="J8">
-        <v>49.74747475</v>
+        <v>49.747474750000002</v>
       </c>
       <c r="K8">
         <v>160</v>
@@ -1107,34 +1231,34 @@
         <v>4420</v>
       </c>
       <c r="P8">
-        <v>1114.253394</v>
+        <v>1114.2533940000001</v>
       </c>
       <c r="Q8">
         <v>99</v>
       </c>
       <c r="S8">
-        <v>49.747475</v>
+        <v>49.747475000000001</v>
       </c>
       <c r="T8">
-        <v>2.239819</v>
+        <v>2.2398189999999998</v>
       </c>
       <c r="U8">
         <v>111</v>
       </c>
       <c r="V8">
-        <v>2.511312</v>
+        <v>2.5113120000000002</v>
       </c>
       <c r="W8">
-        <v>44.369369</v>
+        <v>44.369368999999999</v>
       </c>
       <c r="X8">
         <v>79</v>
       </c>
       <c r="Y8">
-        <v>62.341772</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25">
+        <v>62.341771999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1181,7 +1305,7 @@
         <v>4807</v>
       </c>
       <c r="P9">
-        <v>1030.996463</v>
+        <v>1030.9964629999999</v>
       </c>
       <c r="Q9">
         <v>112</v>
@@ -1199,16 +1323,16 @@
         <v>2.600374</v>
       </c>
       <c r="W9">
-        <v>39.648</v>
+        <v>39.648000000000003</v>
       </c>
       <c r="X9">
         <v>95</v>
       </c>
       <c r="Y9">
-        <v>52.168421</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25">
+        <v>52.168421000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1234,7 +1358,7 @@
         <v>2398</v>
       </c>
       <c r="I10">
-        <v>1.28774</v>
+        <v>1.2877400000000001</v>
       </c>
       <c r="J10">
         <v>46.99038462</v>
@@ -1261,28 +1385,28 @@
         <v>104</v>
       </c>
       <c r="S10">
-        <v>46.990385</v>
+        <v>46.990385000000003</v>
       </c>
       <c r="T10">
-        <v>3.367876</v>
+        <v>3.3678759999999999</v>
       </c>
       <c r="U10">
         <v>124</v>
       </c>
       <c r="V10">
-        <v>4.015544</v>
+        <v>4.0155440000000002</v>
       </c>
       <c r="W10">
-        <v>39.41129</v>
+        <v>39.411290000000001</v>
       </c>
       <c r="X10">
         <v>81</v>
       </c>
       <c r="Y10">
-        <v>60.333333</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25">
+        <v>60.333333000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1311,7 +1435,7 @@
         <v>1.397124</v>
       </c>
       <c r="J11">
-        <v>48.17647059</v>
+        <v>48.176470590000001</v>
       </c>
       <c r="K11">
         <v>160</v>
@@ -1329,25 +1453,25 @@
         <v>4760</v>
       </c>
       <c r="P11">
-        <v>1032.352941</v>
+        <v>1032.3529410000001</v>
       </c>
       <c r="Q11">
         <v>102</v>
       </c>
       <c r="S11">
-        <v>48.176471</v>
+        <v>48.176470999999999</v>
       </c>
       <c r="T11">
-        <v>2.142857</v>
+        <v>2.1428569999999998</v>
       </c>
       <c r="U11">
         <v>107</v>
       </c>
       <c r="V11">
-        <v>2.247899</v>
+        <v>2.2478989999999999</v>
       </c>
       <c r="W11">
-        <v>45.925234</v>
+        <v>45.925234000000003</v>
       </c>
       <c r="X11">
         <v>78</v>
@@ -1356,7 +1480,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1382,10 +1506,10 @@
         <v>4569</v>
       </c>
       <c r="I12">
-        <v>1.395272</v>
+        <v>1.3952720000000001</v>
       </c>
       <c r="J12">
-        <v>33.55367232</v>
+        <v>33.553672319999997</v>
       </c>
       <c r="K12" t="s">
         <v>34</v>
@@ -1409,16 +1533,16 @@
         <v>172</v>
       </c>
       <c r="S12">
-        <v>34.52907</v>
+        <v>34.529069999999997</v>
       </c>
       <c r="T12">
-        <v>2.698039</v>
+        <v>2.6980390000000001</v>
       </c>
       <c r="U12">
         <v>237</v>
       </c>
       <c r="V12">
-        <v>3.717647</v>
+        <v>3.7176469999999999</v>
       </c>
       <c r="W12">
         <v>25.059072</v>
@@ -1427,10 +1551,10 @@
         <v>177</v>
       </c>
       <c r="Y12">
-        <v>33.553672</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25">
+        <v>33.553671999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1456,10 +1580,10 @@
         <v>2980</v>
       </c>
       <c r="I13">
-        <v>1.494295</v>
+        <v>1.4942949999999999</v>
       </c>
       <c r="J13">
-        <v>58.51351351</v>
+        <v>58.513513510000003</v>
       </c>
       <c r="K13" t="s">
         <v>34</v>
@@ -1483,28 +1607,28 @@
         <v>117</v>
       </c>
       <c r="S13">
-        <v>55.512821</v>
+        <v>55.512821000000002</v>
       </c>
       <c r="T13">
-        <v>2.627442</v>
+        <v>2.6274419999999998</v>
       </c>
       <c r="U13">
         <v>143</v>
       </c>
       <c r="V13">
-        <v>3.211318</v>
+        <v>3.2113179999999999</v>
       </c>
       <c r="W13">
-        <v>45.41958</v>
+        <v>45.419580000000003</v>
       </c>
       <c r="X13">
         <v>111</v>
       </c>
       <c r="Y13">
-        <v>58.513514</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25">
+        <v>58.513514000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1566,7 +1690,7 @@
         <v>120</v>
       </c>
       <c r="V14">
-        <v>2.505742</v>
+        <v>2.5057420000000001</v>
       </c>
       <c r="W14">
         <v>56.258333</v>
@@ -1575,10 +1699,10 @@
         <v>107</v>
       </c>
       <c r="Y14">
-        <v>63.093458</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25">
+        <v>63.093457999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1607,7 +1731,7 @@
         <v>1.427308</v>
       </c>
       <c r="J15">
-        <v>54.08264463</v>
+        <v>54.082644629999997</v>
       </c>
       <c r="K15" t="s">
         <v>34</v>
@@ -1631,28 +1755,28 @@
         <v>119</v>
       </c>
       <c r="S15">
-        <v>54.991597</v>
+        <v>54.991596999999999</v>
       </c>
       <c r="T15">
-        <v>2.458678</v>
+        <v>2.4586779999999999</v>
       </c>
       <c r="U15">
         <v>144</v>
       </c>
       <c r="V15">
-        <v>2.975207</v>
+        <v>2.9752070000000002</v>
       </c>
       <c r="W15">
-        <v>45.444444</v>
+        <v>45.444443999999997</v>
       </c>
       <c r="X15">
         <v>121</v>
       </c>
       <c r="Y15">
-        <v>54.082645</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25">
+        <v>54.082644999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1678,10 +1802,10 @@
         <v>4704</v>
       </c>
       <c r="I16">
-        <v>1.174745</v>
+        <v>1.1747449999999999</v>
       </c>
       <c r="J16">
-        <v>82.91764706</v>
+        <v>82.917647059999993</v>
       </c>
       <c r="K16" t="s">
         <v>34</v>
@@ -1705,10 +1829,10 @@
         <v>81</v>
       </c>
       <c r="S16">
-        <v>87.012346</v>
+        <v>87.012345999999994</v>
       </c>
       <c r="T16">
-        <v>1.465798</v>
+        <v>1.4657979999999999</v>
       </c>
       <c r="U16">
         <v>102</v>
@@ -1723,10 +1847,10 @@
         <v>85</v>
       </c>
       <c r="Y16">
-        <v>82.917647</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25">
+        <v>82.917647000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1755,7 +1879,7 @@
         <v>1.147465</v>
       </c>
       <c r="J17">
-        <v>139.79166667</v>
+        <v>139.79166667000001</v>
       </c>
       <c r="K17" t="s">
         <v>34</v>
@@ -1773,16 +1897,16 @@
         <v>4980</v>
       </c>
       <c r="P17">
-        <v>1347.389558</v>
+        <v>1347.3895580000001</v>
       </c>
       <c r="Q17">
         <v>71</v>
       </c>
       <c r="S17">
-        <v>94.507042</v>
+        <v>94.507041999999998</v>
       </c>
       <c r="T17">
-        <v>1.425703</v>
+        <v>1.4257029999999999</v>
       </c>
       <c r="U17">
         <v>81</v>
@@ -1797,10 +1921,10 @@
         <v>48</v>
       </c>
       <c r="Y17">
-        <v>139.791667</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25">
+        <v>139.79166699999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1829,7 +1953,7 @@
         <v>1.359102</v>
       </c>
       <c r="J18">
-        <v>71.58762887</v>
+        <v>71.587628870000003</v>
       </c>
       <c r="K18" t="s">
         <v>34</v>
@@ -1853,28 +1977,28 @@
         <v>97</v>
       </c>
       <c r="S18">
-        <v>71.587629</v>
+        <v>71.587629000000007</v>
       </c>
       <c r="T18">
-        <v>2.081992</v>
+        <v>2.0819920000000001</v>
       </c>
       <c r="U18">
         <v>103</v>
       </c>
       <c r="V18">
-        <v>2.210775</v>
+        <v>2.2107749999999999</v>
       </c>
       <c r="W18">
-        <v>67.417476</v>
+        <v>67.417475999999994</v>
       </c>
       <c r="X18">
         <v>97</v>
       </c>
       <c r="Y18">
-        <v>71.587629</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25">
+        <v>71.587629000000007</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -1900,10 +2024,10 @@
         <v>1573</v>
       </c>
       <c r="I19">
-        <v>1.294342</v>
+        <v>1.2943420000000001</v>
       </c>
       <c r="J19">
-        <v>41.39759036</v>
+        <v>41.397590360000002</v>
       </c>
       <c r="K19" t="s">
         <v>34</v>
@@ -1921,34 +2045,34 @@
         <v>2036</v>
       </c>
       <c r="P19">
-        <v>1687.62279</v>
+        <v>1687.6227899999999</v>
       </c>
       <c r="Q19">
         <v>92</v>
       </c>
       <c r="S19">
-        <v>37.347826</v>
+        <v>37.347825999999998</v>
       </c>
       <c r="T19">
-        <v>4.518664</v>
+        <v>4.5186640000000002</v>
       </c>
       <c r="U19">
         <v>104</v>
       </c>
       <c r="V19">
-        <v>5.108055</v>
+        <v>5.1080550000000002</v>
       </c>
       <c r="W19">
-        <v>33.038462</v>
+        <v>33.038462000000003</v>
       </c>
       <c r="X19">
         <v>83</v>
       </c>
       <c r="Y19">
-        <v>41.39759</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25">
+        <v>41.397590000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -1977,7 +2101,7 @@
         <v>1.426825</v>
       </c>
       <c r="J20">
-        <v>51.63157895</v>
+        <v>51.631578949999998</v>
       </c>
       <c r="K20" t="s">
         <v>34</v>
@@ -1995,34 +2119,34 @@
         <v>4085</v>
       </c>
       <c r="P20">
-        <v>1200.734394</v>
+        <v>1200.7343940000001</v>
       </c>
       <c r="Q20">
         <v>102</v>
       </c>
       <c r="S20">
-        <v>48.088235</v>
+        <v>48.088234999999997</v>
       </c>
       <c r="T20">
-        <v>2.49694</v>
+        <v>2.4969399999999999</v>
       </c>
       <c r="U20">
         <v>112</v>
       </c>
       <c r="V20">
-        <v>2.741738</v>
+        <v>2.7417379999999998</v>
       </c>
       <c r="W20">
-        <v>43.794643</v>
+        <v>43.794643000000001</v>
       </c>
       <c r="X20">
         <v>95</v>
       </c>
       <c r="Y20">
-        <v>51.631579</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25">
+        <v>51.631579000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -2051,7 +2175,7 @@
         <v>1.534489</v>
       </c>
       <c r="J21">
-        <v>40.44537815</v>
+        <v>40.445378150000003</v>
       </c>
       <c r="K21" t="s">
         <v>34</v>
@@ -2069,13 +2193,13 @@
         <v>4160</v>
       </c>
       <c r="P21">
-        <v>1156.971154</v>
+        <v>1156.9711540000001</v>
       </c>
       <c r="Q21">
         <v>137</v>
       </c>
       <c r="S21">
-        <v>35.131387</v>
+        <v>35.131386999999997</v>
       </c>
       <c r="T21">
         <v>3.293269</v>
@@ -2084,19 +2208,19 @@
         <v>152</v>
       </c>
       <c r="V21">
-        <v>3.653846</v>
+        <v>3.6538460000000001</v>
       </c>
       <c r="W21">
-        <v>31.664474</v>
+        <v>31.664473999999998</v>
       </c>
       <c r="X21">
         <v>119</v>
       </c>
       <c r="Y21">
-        <v>40.445378</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25">
+        <v>40.445377999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -2122,7 +2246,7 @@
         <v>3099</v>
       </c>
       <c r="I22">
-        <v>1.384318</v>
+        <v>1.3843179999999999</v>
       </c>
       <c r="J22">
         <v>55.04819277</v>
@@ -2143,34 +2267,34 @@
         <v>4290</v>
       </c>
       <c r="P22">
-        <v>1065.034965</v>
+        <v>1065.0349650000001</v>
       </c>
       <c r="Q22">
         <v>93</v>
       </c>
       <c r="S22">
-        <v>49.129032</v>
+        <v>49.129032000000002</v>
       </c>
       <c r="T22">
-        <v>2.167832</v>
+        <v>2.1678320000000002</v>
       </c>
       <c r="U22">
         <v>113</v>
       </c>
       <c r="V22">
-        <v>2.634033</v>
+        <v>2.6340330000000001</v>
       </c>
       <c r="W22">
-        <v>40.433628</v>
+        <v>40.433627999999999</v>
       </c>
       <c r="X22">
         <v>83</v>
       </c>
       <c r="Y22">
-        <v>55.048193</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25">
+        <v>55.048192999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -2196,7 +2320,7 @@
         <v>2484</v>
       </c>
       <c r="I23">
-        <v>1.6719</v>
+        <v>1.6718999999999999</v>
       </c>
       <c r="J23">
         <v>143.63888889</v>
@@ -2217,34 +2341,34 @@
         <v>4153</v>
       </c>
       <c r="P23">
-        <v>1245.124007</v>
+        <v>1245.1240069999999</v>
       </c>
       <c r="Q23">
         <v>52</v>
       </c>
       <c r="S23">
-        <v>99.442308</v>
+        <v>99.442307999999997</v>
       </c>
       <c r="T23">
-        <v>1.252107</v>
+        <v>1.2521070000000001</v>
       </c>
       <c r="U23">
         <v>56</v>
       </c>
       <c r="V23">
-        <v>1.348423</v>
+        <v>1.3484229999999999</v>
       </c>
       <c r="W23">
-        <v>92.339286</v>
+        <v>92.339286000000001</v>
       </c>
       <c r="X23">
         <v>36</v>
       </c>
       <c r="Y23">
-        <v>143.638889</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25">
+        <v>143.63888900000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -2273,7 +2397,7 @@
         <v>1.57548</v>
       </c>
       <c r="J24">
-        <v>64.67901235</v>
+        <v>64.679012349999994</v>
       </c>
       <c r="K24" t="s">
         <v>34</v>
@@ -2306,7 +2430,7 @@
         <v>104</v>
       </c>
       <c r="V24">
-        <v>2.752779</v>
+        <v>2.7527789999999999</v>
       </c>
       <c r="W24">
         <v>50.375</v>
@@ -2318,7 +2442,7 @@
         <v>64.679012</v>
       </c>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -2347,7 +2471,7 @@
         <v>1.205392</v>
       </c>
       <c r="J25">
-        <v>46.50746269</v>
+        <v>46.507462689999997</v>
       </c>
       <c r="K25" t="s">
         <v>34</v>
@@ -2365,34 +2489,34 @@
         <v>1878</v>
       </c>
       <c r="P25">
-        <v>1659.211928</v>
+        <v>1659.2119279999999</v>
       </c>
       <c r="Q25">
         <v>75</v>
       </c>
       <c r="S25">
-        <v>41.546667</v>
+        <v>41.546666999999999</v>
       </c>
       <c r="T25">
-        <v>3.99361</v>
+        <v>3.9936099999999999</v>
       </c>
       <c r="U25">
         <v>84</v>
       </c>
       <c r="V25">
-        <v>4.472843</v>
+        <v>4.4728430000000001</v>
       </c>
       <c r="W25">
-        <v>37.095238</v>
+        <v>37.095238000000002</v>
       </c>
       <c r="X25">
         <v>67</v>
       </c>
       <c r="Y25">
-        <v>46.507463</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25">
+        <v>46.507463000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -2418,10 +2542,10 @@
         <v>263</v>
       </c>
       <c r="I26">
-        <v>1.038023</v>
+        <v>1.0380229999999999</v>
       </c>
       <c r="J26">
-        <v>77.33333333</v>
+        <v>77.333333330000002</v>
       </c>
       <c r="K26" t="s">
         <v>34</v>
@@ -2439,7 +2563,7 @@
         <v>273</v>
       </c>
       <c r="P26">
-        <v>1699.6337</v>
+        <v>1699.6337000000001</v>
       </c>
       <c r="Q26">
         <v>5</v>
@@ -2454,19 +2578,19 @@
         <v>6</v>
       </c>
       <c r="V26">
-        <v>2.197802</v>
+        <v>2.1978019999999998</v>
       </c>
       <c r="W26">
-        <v>77.333333</v>
+        <v>77.333332999999996</v>
       </c>
       <c r="X26">
         <v>6</v>
       </c>
       <c r="Y26">
-        <v>77.333333</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25">
+        <v>77.333332999999996</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -2516,7 +2640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -2566,7 +2690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -2592,10 +2716,10 @@
         <v>1434</v>
       </c>
       <c r="I29">
-        <v>1.407252</v>
+        <v>1.4072519999999999</v>
       </c>
       <c r="J29">
-        <v>85.91666667</v>
+        <v>85.916666669999998</v>
       </c>
       <c r="K29" t="s">
         <v>34</v>
@@ -2628,19 +2752,19 @@
         <v>31</v>
       </c>
       <c r="V29">
-        <v>1.536174</v>
+        <v>1.5361739999999999</v>
       </c>
       <c r="W29">
-        <v>66.516129</v>
+        <v>66.516129000000006</v>
       </c>
       <c r="X29">
         <v>24</v>
       </c>
       <c r="Y29">
-        <v>85.916667</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25">
+        <v>85.916667000000004</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -2687,13 +2811,13 @@
         <v>1445</v>
       </c>
       <c r="P30">
-        <v>1537.024221</v>
+        <v>1537.0242209999999</v>
       </c>
       <c r="Q30">
         <v>49</v>
       </c>
       <c r="S30">
-        <v>45.326531</v>
+        <v>45.326531000000003</v>
       </c>
       <c r="T30">
         <v>3.391003</v>
@@ -2702,10 +2826,10 @@
         <v>58</v>
       </c>
       <c r="V30">
-        <v>4.013841</v>
+        <v>4.0138410000000002</v>
       </c>
       <c r="W30">
-        <v>38.293103</v>
+        <v>38.293103000000002</v>
       </c>
       <c r="X30">
         <v>50</v>
@@ -2714,18 +2838,1911 @@
         <v>44.42</v>
       </c>
     </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" t="s">
+        <v>38</v>
+      </c>
+      <c r="E31" t="s">
+        <v>29</v>
+      </c>
+      <c r="F31">
+        <v>17</v>
+      </c>
+      <c r="G31" t="s">
+        <v>49</v>
+      </c>
+      <c r="H31">
+        <v>2405</v>
+      </c>
+      <c r="I31">
+        <v>1.496882</v>
+      </c>
+      <c r="J31">
+        <v>299.58823529</v>
+      </c>
+      <c r="K31" t="s">
+        <v>34</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>5093</v>
+      </c>
+      <c r="N31" t="s">
+        <v>65</v>
+      </c>
+      <c r="O31">
+        <v>3600</v>
+      </c>
+      <c r="P31">
+        <v>1414.7222220000001</v>
+      </c>
+      <c r="Q31">
+        <v>52</v>
+      </c>
+      <c r="S31">
+        <v>97.942307999999997</v>
+      </c>
+      <c r="T31">
+        <v>1.4444440000000001</v>
+      </c>
+      <c r="U31">
+        <v>69</v>
+      </c>
+      <c r="V31">
+        <v>1.9166669999999999</v>
+      </c>
+      <c r="W31">
+        <v>73.811593999999999</v>
+      </c>
+      <c r="X31">
+        <v>17</v>
+      </c>
+      <c r="Y31">
+        <v>299.588235</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" t="s">
+        <v>119</v>
+      </c>
+      <c r="D32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E32" t="s">
+        <v>29</v>
+      </c>
+      <c r="F32">
+        <v>139</v>
+      </c>
+      <c r="G32" t="s">
+        <v>39</v>
+      </c>
+      <c r="H32">
+        <v>2587</v>
+      </c>
+      <c r="I32">
+        <v>1.219946</v>
+      </c>
+      <c r="J32">
+        <v>45.381294959999998</v>
+      </c>
+      <c r="K32" t="s">
+        <v>34</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>6308</v>
+      </c>
+      <c r="N32" t="s">
+        <v>118</v>
+      </c>
+      <c r="O32">
+        <v>3156</v>
+      </c>
+      <c r="P32">
+        <v>1998.732573</v>
+      </c>
+      <c r="Q32">
+        <v>139</v>
+      </c>
+      <c r="S32">
+        <v>45.381295000000001</v>
+      </c>
+      <c r="T32">
+        <v>4.4043089999999996</v>
+      </c>
+      <c r="U32">
+        <v>149</v>
+      </c>
+      <c r="V32">
+        <v>4.7211660000000002</v>
+      </c>
+      <c r="W32">
+        <v>42.335569999999997</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" t="s">
+        <v>117</v>
+      </c>
+      <c r="D33" t="s">
+        <v>81</v>
+      </c>
+      <c r="E33" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33">
+        <v>7</v>
+      </c>
+      <c r="G33" t="s">
+        <v>49</v>
+      </c>
+      <c r="H33">
+        <v>873</v>
+      </c>
+      <c r="I33">
+        <v>1.2050399999999999</v>
+      </c>
+      <c r="J33">
+        <v>135.57142856999999</v>
+      </c>
+      <c r="K33" t="s">
+        <v>34</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>949</v>
+      </c>
+      <c r="N33" t="s">
+        <v>114</v>
+      </c>
+      <c r="O33">
+        <v>1052</v>
+      </c>
+      <c r="P33">
+        <v>902.09125500000005</v>
+      </c>
+      <c r="Q33">
+        <v>10</v>
+      </c>
+      <c r="S33">
+        <v>94.9</v>
+      </c>
+      <c r="T33">
+        <v>0.95057000000000003</v>
+      </c>
+      <c r="U33">
+        <v>11</v>
+      </c>
+      <c r="V33">
+        <v>1.0456270000000001</v>
+      </c>
+      <c r="W33">
+        <v>86.272727000000003</v>
+      </c>
+      <c r="X33">
+        <v>7</v>
+      </c>
+      <c r="Y33">
+        <v>135.57142899999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" t="s">
+        <v>116</v>
+      </c>
+      <c r="D34" t="s">
+        <v>81</v>
+      </c>
+      <c r="E34" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34">
+        <v>63</v>
+      </c>
+      <c r="G34" t="s">
+        <v>39</v>
+      </c>
+      <c r="H34">
+        <v>5399</v>
+      </c>
+      <c r="I34">
+        <v>1.3421000000000001</v>
+      </c>
+      <c r="J34">
+        <v>92.190476189999998</v>
+      </c>
+      <c r="K34" t="s">
+        <v>34</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>5808</v>
+      </c>
+      <c r="N34" t="s">
+        <v>103</v>
+      </c>
+      <c r="O34">
+        <v>7246</v>
+      </c>
+      <c r="P34">
+        <v>801.54567999999995</v>
+      </c>
+      <c r="Q34">
+        <v>63</v>
+      </c>
+      <c r="S34">
+        <v>92.190476000000004</v>
+      </c>
+      <c r="T34">
+        <v>0.86944500000000002</v>
+      </c>
+      <c r="U34">
+        <v>68</v>
+      </c>
+      <c r="V34">
+        <v>0.93844899999999998</v>
+      </c>
+      <c r="W34">
+        <v>85.411765000000003</v>
+      </c>
+      <c r="X34">
+        <v>49</v>
+      </c>
+      <c r="Y34">
+        <v>118.530612</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" t="s">
+        <v>115</v>
+      </c>
+      <c r="D35" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" t="s">
+        <v>29</v>
+      </c>
+      <c r="F35">
+        <v>78</v>
+      </c>
+      <c r="G35" t="s">
+        <v>49</v>
+      </c>
+      <c r="H35">
+        <v>2867</v>
+      </c>
+      <c r="I35">
+        <v>1.3557729999999999</v>
+      </c>
+      <c r="J35">
+        <v>54.11538462</v>
+      </c>
+      <c r="K35" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>4221</v>
+      </c>
+      <c r="N35" t="s">
+        <v>114</v>
+      </c>
+      <c r="O35">
+        <v>3887</v>
+      </c>
+      <c r="P35">
+        <v>1085.9274499999999</v>
+      </c>
+      <c r="Q35">
+        <v>121</v>
+      </c>
+      <c r="S35">
+        <v>34.884298000000001</v>
+      </c>
+      <c r="T35">
+        <v>3.1129410000000002</v>
+      </c>
+      <c r="U35">
+        <v>121</v>
+      </c>
+      <c r="V35">
+        <v>3.1129410000000002</v>
+      </c>
+      <c r="W35">
+        <v>34.884298000000001</v>
+      </c>
+      <c r="X35">
+        <v>78</v>
+      </c>
+      <c r="Y35">
+        <v>54.115385000000003</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" t="s">
+        <v>113</v>
+      </c>
+      <c r="D36" t="s">
+        <v>38</v>
+      </c>
+      <c r="E36" t="s">
+        <v>29</v>
+      </c>
+      <c r="F36">
+        <v>155</v>
+      </c>
+      <c r="G36" t="s">
+        <v>39</v>
+      </c>
+      <c r="H36">
+        <v>4127</v>
+      </c>
+      <c r="I36">
+        <v>1.3283259999999999</v>
+      </c>
+      <c r="J36">
+        <v>39.193548389999997</v>
+      </c>
+      <c r="K36" t="s">
+        <v>34</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>6075</v>
+      </c>
+      <c r="N36" t="s">
+        <v>112</v>
+      </c>
+      <c r="O36">
+        <v>5482</v>
+      </c>
+      <c r="P36">
+        <v>1108.1722</v>
+      </c>
+      <c r="Q36">
+        <v>155</v>
+      </c>
+      <c r="S36">
+        <v>39.193548</v>
+      </c>
+      <c r="T36">
+        <v>2.8274349999999999</v>
+      </c>
+      <c r="U36">
+        <v>167</v>
+      </c>
+      <c r="V36">
+        <v>3.0463330000000002</v>
+      </c>
+      <c r="W36">
+        <v>36.377246</v>
+      </c>
+      <c r="X36">
+        <v>83</v>
+      </c>
+      <c r="Y36">
+        <v>73.192770999999993</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37" t="s">
+        <v>111</v>
+      </c>
+      <c r="D37" t="s">
+        <v>38</v>
+      </c>
+      <c r="E37" t="s">
+        <v>29</v>
+      </c>
+      <c r="F37">
+        <v>87</v>
+      </c>
+      <c r="G37" t="s">
+        <v>49</v>
+      </c>
+      <c r="H37">
+        <v>3063</v>
+      </c>
+      <c r="I37">
+        <v>1.47078</v>
+      </c>
+      <c r="J37">
+        <v>78.114942529999993</v>
+      </c>
+      <c r="K37" t="s">
+        <v>34</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>6796</v>
+      </c>
+      <c r="N37" t="s">
+        <v>63</v>
+      </c>
+      <c r="O37">
+        <v>4505</v>
+      </c>
+      <c r="P37">
+        <v>1508.5460599999999</v>
+      </c>
+      <c r="Q37">
+        <v>85</v>
+      </c>
+      <c r="S37">
+        <v>79.952940999999996</v>
+      </c>
+      <c r="T37">
+        <v>1.886792</v>
+      </c>
+      <c r="U37">
+        <v>103</v>
+      </c>
+      <c r="V37">
+        <v>2.286349</v>
+      </c>
+      <c r="W37">
+        <v>65.980582999999996</v>
+      </c>
+      <c r="X37">
+        <v>87</v>
+      </c>
+      <c r="Y37">
+        <v>78.114942999999997</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" t="s">
+        <v>71</v>
+      </c>
+      <c r="D38" t="s">
+        <v>38</v>
+      </c>
+      <c r="E38" t="s">
+        <v>29</v>
+      </c>
+      <c r="F38">
+        <v>256</v>
+      </c>
+      <c r="G38" t="s">
+        <v>49</v>
+      </c>
+      <c r="H38">
+        <v>6106</v>
+      </c>
+      <c r="I38">
+        <v>1.339011</v>
+      </c>
+      <c r="J38">
+        <v>56.625</v>
+      </c>
+      <c r="K38" t="s">
+        <v>34</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>14496</v>
+      </c>
+      <c r="N38" t="s">
+        <v>110</v>
+      </c>
+      <c r="O38">
+        <v>8176</v>
+      </c>
+      <c r="P38">
+        <v>1772.9941289999999</v>
+      </c>
+      <c r="Q38">
+        <v>260</v>
+      </c>
+      <c r="S38">
+        <v>55.753846000000003</v>
+      </c>
+      <c r="T38">
+        <v>3.1800389999999998</v>
+      </c>
+      <c r="U38">
+        <v>298</v>
+      </c>
+      <c r="V38">
+        <v>3.6448140000000002</v>
+      </c>
+      <c r="W38">
+        <v>48.644295</v>
+      </c>
+      <c r="X38">
+        <v>256</v>
+      </c>
+      <c r="Y38">
+        <v>56.625</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" t="s">
+        <v>109</v>
+      </c>
+      <c r="D39" t="s">
+        <v>28</v>
+      </c>
+      <c r="E39" t="s">
+        <v>29</v>
+      </c>
+      <c r="F39">
+        <v>24</v>
+      </c>
+      <c r="G39" t="s">
+        <v>39</v>
+      </c>
+      <c r="H39">
+        <v>890</v>
+      </c>
+      <c r="I39">
+        <v>1.051685</v>
+      </c>
+      <c r="J39">
+        <v>69.041666669999998</v>
+      </c>
+      <c r="K39" t="s">
+        <v>34</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>1657</v>
+      </c>
+      <c r="N39" t="s">
+        <v>79</v>
+      </c>
+      <c r="O39">
+        <v>936</v>
+      </c>
+      <c r="P39">
+        <v>1770.299145</v>
+      </c>
+      <c r="Q39">
+        <v>24</v>
+      </c>
+      <c r="S39">
+        <v>69.041667000000004</v>
+      </c>
+      <c r="T39">
+        <v>2.5641029999999998</v>
+      </c>
+      <c r="U39">
+        <v>25</v>
+      </c>
+      <c r="V39">
+        <v>2.6709399999999999</v>
+      </c>
+      <c r="W39">
+        <v>66.28</v>
+      </c>
+      <c r="X39">
+        <v>6</v>
+      </c>
+      <c r="Y39">
+        <v>276.16666700000002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" t="s">
+        <v>108</v>
+      </c>
+      <c r="D40" t="s">
+        <v>38</v>
+      </c>
+      <c r="E40" t="s">
+        <v>29</v>
+      </c>
+      <c r="F40">
+        <v>25</v>
+      </c>
+      <c r="G40" t="s">
+        <v>49</v>
+      </c>
+      <c r="H40">
+        <v>3795</v>
+      </c>
+      <c r="I40">
+        <v>1.435573</v>
+      </c>
+      <c r="J40">
+        <v>252.56</v>
+      </c>
+      <c r="K40" t="s">
+        <v>34</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>6314</v>
+      </c>
+      <c r="N40" t="s">
+        <v>107</v>
+      </c>
+      <c r="O40">
+        <v>5448</v>
+      </c>
+      <c r="P40">
+        <v>1158.957416</v>
+      </c>
+      <c r="Q40">
+        <v>180</v>
+      </c>
+      <c r="S40">
+        <v>35.077778000000002</v>
+      </c>
+      <c r="T40">
+        <v>3.3039649999999998</v>
+      </c>
+      <c r="U40">
+        <v>188</v>
+      </c>
+      <c r="V40">
+        <v>3.4508079999999999</v>
+      </c>
+      <c r="W40">
+        <v>33.585106000000003</v>
+      </c>
+      <c r="X40">
+        <v>25</v>
+      </c>
+      <c r="Y40">
+        <v>252.56</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" t="s">
+        <v>106</v>
+      </c>
+      <c r="D41" t="s">
+        <v>38</v>
+      </c>
+      <c r="E41" t="s">
+        <v>29</v>
+      </c>
+      <c r="F41">
+        <v>99</v>
+      </c>
+      <c r="G41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H41">
+        <v>4324</v>
+      </c>
+      <c r="I41">
+        <v>1.48543</v>
+      </c>
+      <c r="J41">
+        <v>59.131313130000002</v>
+      </c>
+      <c r="K41" t="s">
+        <v>34</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>5854</v>
+      </c>
+      <c r="N41" t="s">
+        <v>105</v>
+      </c>
+      <c r="O41">
+        <v>6423</v>
+      </c>
+      <c r="P41">
+        <v>911.41211299999998</v>
+      </c>
+      <c r="Q41">
+        <v>99</v>
+      </c>
+      <c r="S41">
+        <v>59.131312999999999</v>
+      </c>
+      <c r="T41">
+        <v>1.541336</v>
+      </c>
+      <c r="U41">
+        <v>131</v>
+      </c>
+      <c r="V41">
+        <v>2.0395449999999999</v>
+      </c>
+      <c r="W41">
+        <v>44.687023000000003</v>
+      </c>
+      <c r="X41">
+        <v>85</v>
+      </c>
+      <c r="Y41">
+        <v>68.870587999999998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" t="s">
+        <v>104</v>
+      </c>
+      <c r="D42" t="s">
+        <v>81</v>
+      </c>
+      <c r="E42" t="s">
+        <v>29</v>
+      </c>
+      <c r="F42">
+        <v>151</v>
+      </c>
+      <c r="G42" t="s">
+        <v>39</v>
+      </c>
+      <c r="H42">
+        <v>2711</v>
+      </c>
+      <c r="I42">
+        <v>1.2364440000000001</v>
+      </c>
+      <c r="J42">
+        <v>41.562913909999999</v>
+      </c>
+      <c r="K42" t="s">
+        <v>34</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>6276</v>
+      </c>
+      <c r="N42" t="s">
+        <v>103</v>
+      </c>
+      <c r="O42">
+        <v>3352</v>
+      </c>
+      <c r="P42">
+        <v>1872.315036</v>
+      </c>
+      <c r="Q42">
+        <v>151</v>
+      </c>
+      <c r="S42">
+        <v>41.562913999999999</v>
+      </c>
+      <c r="T42">
+        <v>4.5047730000000001</v>
+      </c>
+      <c r="U42">
+        <v>167</v>
+      </c>
+      <c r="V42">
+        <v>4.9821</v>
+      </c>
+      <c r="W42">
+        <v>37.580838</v>
+      </c>
+      <c r="X42">
+        <v>125</v>
+      </c>
+      <c r="Y42">
+        <v>50.207999999999998</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43" t="s">
+        <v>102</v>
+      </c>
+      <c r="D43" t="s">
+        <v>81</v>
+      </c>
+      <c r="E43" t="s">
+        <v>29</v>
+      </c>
+      <c r="F43">
+        <v>155</v>
+      </c>
+      <c r="G43" t="s">
+        <v>39</v>
+      </c>
+      <c r="H43">
+        <v>2997</v>
+      </c>
+      <c r="I43">
+        <v>1.2118789999999999</v>
+      </c>
+      <c r="J43">
+        <v>37.84516129</v>
+      </c>
+      <c r="K43" t="s">
+        <v>34</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>5866</v>
+      </c>
+      <c r="N43" t="s">
+        <v>95</v>
+      </c>
+      <c r="O43">
+        <v>3632</v>
+      </c>
+      <c r="P43">
+        <v>1615.0881059999999</v>
+      </c>
+      <c r="Q43">
+        <v>155</v>
+      </c>
+      <c r="S43">
+        <v>37.845160999999997</v>
+      </c>
+      <c r="T43">
+        <v>4.2676210000000001</v>
+      </c>
+      <c r="U43">
+        <v>156</v>
+      </c>
+      <c r="V43">
+        <v>4.2951540000000001</v>
+      </c>
+      <c r="W43">
+        <v>37.602564000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" t="s">
+        <v>101</v>
+      </c>
+      <c r="D44" t="s">
+        <v>38</v>
+      </c>
+      <c r="E44" t="s">
+        <v>29</v>
+      </c>
+      <c r="F44">
+        <v>102</v>
+      </c>
+      <c r="G44" t="s">
+        <v>39</v>
+      </c>
+      <c r="H44">
+        <v>5495</v>
+      </c>
+      <c r="I44">
+        <v>1.4041859999999999</v>
+      </c>
+      <c r="J44">
+        <v>61.89215686</v>
+      </c>
+      <c r="K44" t="s">
+        <v>34</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>6313</v>
+      </c>
+      <c r="N44" t="s">
+        <v>100</v>
+      </c>
+      <c r="O44">
+        <v>7716</v>
+      </c>
+      <c r="P44">
+        <v>818.17003599999998</v>
+      </c>
+      <c r="Q44">
+        <v>102</v>
+      </c>
+      <c r="S44">
+        <v>61.892156999999997</v>
+      </c>
+      <c r="T44">
+        <v>1.321928</v>
+      </c>
+      <c r="U44">
+        <v>107</v>
+      </c>
+      <c r="V44">
+        <v>1.3867290000000001</v>
+      </c>
+      <c r="W44">
+        <v>59</v>
+      </c>
+      <c r="X44">
+        <v>48</v>
+      </c>
+      <c r="Y44">
+        <v>131.52083300000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>25</v>
+      </c>
+      <c r="B45" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45" t="s">
+        <v>99</v>
+      </c>
+      <c r="D45" t="s">
+        <v>81</v>
+      </c>
+      <c r="E45" t="s">
+        <v>29</v>
+      </c>
+      <c r="F45">
+        <v>195</v>
+      </c>
+      <c r="G45" t="s">
+        <v>39</v>
+      </c>
+      <c r="H45">
+        <v>3240</v>
+      </c>
+      <c r="I45">
+        <v>1.166358</v>
+      </c>
+      <c r="J45">
+        <v>29.533333330000001</v>
+      </c>
+      <c r="K45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>5759</v>
+      </c>
+      <c r="N45" t="s">
+        <v>86</v>
+      </c>
+      <c r="O45">
+        <v>3779</v>
+      </c>
+      <c r="P45">
+        <v>1523.948134</v>
+      </c>
+      <c r="Q45">
+        <v>195</v>
+      </c>
+      <c r="S45">
+        <v>29.533332999999999</v>
+      </c>
+      <c r="T45">
+        <v>5.1600950000000001</v>
+      </c>
+      <c r="U45">
+        <v>200</v>
+      </c>
+      <c r="V45">
+        <v>5.2924049999999996</v>
+      </c>
+      <c r="W45">
+        <v>28.795000000000002</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" t="s">
+        <v>98</v>
+      </c>
+      <c r="D46" t="s">
+        <v>38</v>
+      </c>
+      <c r="E46" t="s">
+        <v>29</v>
+      </c>
+      <c r="F46">
+        <v>192</v>
+      </c>
+      <c r="G46" t="s">
+        <v>39</v>
+      </c>
+      <c r="H46">
+        <v>3329</v>
+      </c>
+      <c r="I46">
+        <v>1.4079299999999999</v>
+      </c>
+      <c r="J46">
+        <v>33.479166669999998</v>
+      </c>
+      <c r="K46" t="s">
+        <v>34</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>6428</v>
+      </c>
+      <c r="N46" t="s">
+        <v>97</v>
+      </c>
+      <c r="O46">
+        <v>4687</v>
+      </c>
+      <c r="P46">
+        <v>1371.452955</v>
+      </c>
+      <c r="Q46">
+        <v>192</v>
+      </c>
+      <c r="S46">
+        <v>33.479166999999997</v>
+      </c>
+      <c r="T46">
+        <v>4.0964369999999999</v>
+      </c>
+      <c r="U46">
+        <v>211</v>
+      </c>
+      <c r="V46">
+        <v>4.5018140000000004</v>
+      </c>
+      <c r="W46">
+        <v>30.464455000000001</v>
+      </c>
+      <c r="X46">
+        <v>174</v>
+      </c>
+      <c r="Y46">
+        <v>36.942529</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>25</v>
+      </c>
+      <c r="B47" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" t="s">
+        <v>96</v>
+      </c>
+      <c r="D47" t="s">
+        <v>81</v>
+      </c>
+      <c r="E47" t="s">
+        <v>29</v>
+      </c>
+      <c r="F47">
+        <v>89</v>
+      </c>
+      <c r="G47" t="s">
+        <v>39</v>
+      </c>
+      <c r="H47">
+        <v>3595</v>
+      </c>
+      <c r="I47">
+        <v>1.275104</v>
+      </c>
+      <c r="J47">
+        <v>69.146067419999994</v>
+      </c>
+      <c r="K47" t="s">
+        <v>34</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>6154</v>
+      </c>
+      <c r="N47" t="s">
+        <v>95</v>
+      </c>
+      <c r="O47">
+        <v>4584</v>
+      </c>
+      <c r="P47">
+        <v>1342.495637</v>
+      </c>
+      <c r="Q47">
+        <v>89</v>
+      </c>
+      <c r="S47">
+        <v>69.146067000000002</v>
+      </c>
+      <c r="T47">
+        <v>1.9415359999999999</v>
+      </c>
+      <c r="U47">
+        <v>96</v>
+      </c>
+      <c r="V47">
+        <v>2.0942409999999998</v>
+      </c>
+      <c r="W47">
+        <v>64.104167000000004</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48" t="s">
+        <v>38</v>
+      </c>
+      <c r="E48" t="s">
+        <v>29</v>
+      </c>
+      <c r="F48">
+        <v>107</v>
+      </c>
+      <c r="G48" t="s">
+        <v>39</v>
+      </c>
+      <c r="H48">
+        <v>1744</v>
+      </c>
+      <c r="I48">
+        <v>1.1622710000000001</v>
+      </c>
+      <c r="J48">
+        <v>57.990654210000002</v>
+      </c>
+      <c r="K48" t="s">
+        <v>34</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>6205</v>
+      </c>
+      <c r="N48" t="s">
+        <v>93</v>
+      </c>
+      <c r="O48">
+        <v>2027</v>
+      </c>
+      <c r="P48">
+        <v>3061.1741489999999</v>
+      </c>
+      <c r="Q48">
+        <v>107</v>
+      </c>
+      <c r="S48">
+        <v>57.990653999999999</v>
+      </c>
+      <c r="T48">
+        <v>5.2787369999999996</v>
+      </c>
+      <c r="U48">
+        <v>111</v>
+      </c>
+      <c r="V48">
+        <v>5.4760730000000004</v>
+      </c>
+      <c r="W48">
+        <v>55.900900999999998</v>
+      </c>
+      <c r="X48">
+        <v>2</v>
+      </c>
+      <c r="Y48">
+        <v>3102.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>25</v>
+      </c>
+      <c r="B49" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" t="s">
+        <v>92</v>
+      </c>
+      <c r="D49" t="s">
+        <v>81</v>
+      </c>
+      <c r="E49" t="s">
+        <v>29</v>
+      </c>
+      <c r="F49">
+        <v>104</v>
+      </c>
+      <c r="G49" t="s">
+        <v>39</v>
+      </c>
+      <c r="H49">
+        <v>4068</v>
+      </c>
+      <c r="I49">
+        <v>1.3547199999999999</v>
+      </c>
+      <c r="J49">
+        <v>57.32692308</v>
+      </c>
+      <c r="K49" t="s">
+        <v>34</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>5962</v>
+      </c>
+      <c r="N49" t="s">
+        <v>91</v>
+      </c>
+      <c r="O49">
+        <v>5511</v>
+      </c>
+      <c r="P49">
+        <v>1081.836327</v>
+      </c>
+      <c r="Q49">
+        <v>104</v>
+      </c>
+      <c r="S49">
+        <v>57.326923000000001</v>
+      </c>
+      <c r="T49">
+        <v>1.887135</v>
+      </c>
+      <c r="U49">
+        <v>110</v>
+      </c>
+      <c r="V49">
+        <v>1.996008</v>
+      </c>
+      <c r="W49">
+        <v>54.2</v>
+      </c>
+      <c r="X49">
+        <v>64</v>
+      </c>
+      <c r="Y49">
+        <v>93.15625</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" t="s">
+        <v>90</v>
+      </c>
+      <c r="D50" t="s">
+        <v>28</v>
+      </c>
+      <c r="E50" t="s">
+        <v>29</v>
+      </c>
+      <c r="F50">
+        <v>83</v>
+      </c>
+      <c r="G50" t="s">
+        <v>39</v>
+      </c>
+      <c r="H50">
+        <v>3873</v>
+      </c>
+      <c r="I50">
+        <v>1.1962299999999999</v>
+      </c>
+      <c r="J50">
+        <v>65.710843370000006</v>
+      </c>
+      <c r="K50" t="s">
+        <v>34</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>5454</v>
+      </c>
+      <c r="N50" t="s">
+        <v>89</v>
+      </c>
+      <c r="O50">
+        <v>4633</v>
+      </c>
+      <c r="P50">
+        <v>1177.206993</v>
+      </c>
+      <c r="Q50">
+        <v>83</v>
+      </c>
+      <c r="S50">
+        <v>65.710842999999997</v>
+      </c>
+      <c r="T50">
+        <v>1.791496</v>
+      </c>
+      <c r="U50">
+        <v>85</v>
+      </c>
+      <c r="V50">
+        <v>1.8346640000000001</v>
+      </c>
+      <c r="W50">
+        <v>64.164705999999995</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>25</v>
+      </c>
+      <c r="B51" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" t="s">
+        <v>32</v>
+      </c>
+      <c r="D51" t="s">
+        <v>81</v>
+      </c>
+      <c r="E51" t="s">
+        <v>29</v>
+      </c>
+      <c r="F51">
+        <v>75</v>
+      </c>
+      <c r="G51" t="s">
+        <v>39</v>
+      </c>
+      <c r="H51">
+        <v>3555</v>
+      </c>
+      <c r="I51">
+        <v>1.2351620000000001</v>
+      </c>
+      <c r="J51">
+        <v>77.933333329999996</v>
+      </c>
+      <c r="K51" t="s">
+        <v>34</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>5845</v>
+      </c>
+      <c r="N51" t="s">
+        <v>88</v>
+      </c>
+      <c r="O51">
+        <v>4391</v>
+      </c>
+      <c r="P51">
+        <v>1331.1318610000001</v>
+      </c>
+      <c r="Q51">
+        <v>75</v>
+      </c>
+      <c r="S51">
+        <v>77.933333000000005</v>
+      </c>
+      <c r="T51">
+        <v>1.7080390000000001</v>
+      </c>
+      <c r="U51">
+        <v>79</v>
+      </c>
+      <c r="V51">
+        <v>1.7991349999999999</v>
+      </c>
+      <c r="W51">
+        <v>73.987341999999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>25</v>
+      </c>
+      <c r="B52" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" t="s">
+        <v>87</v>
+      </c>
+      <c r="D52" t="s">
+        <v>81</v>
+      </c>
+      <c r="E52" t="s">
+        <v>29</v>
+      </c>
+      <c r="F52">
+        <v>76</v>
+      </c>
+      <c r="G52" t="s">
+        <v>39</v>
+      </c>
+      <c r="H52">
+        <v>3345</v>
+      </c>
+      <c r="I52">
+        <v>1.2083710000000001</v>
+      </c>
+      <c r="J52">
+        <v>76.434210530000001</v>
+      </c>
+      <c r="K52" t="s">
+        <v>34</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>5809</v>
+      </c>
+      <c r="N52" t="s">
+        <v>86</v>
+      </c>
+      <c r="O52">
+        <v>4042</v>
+      </c>
+      <c r="P52">
+        <v>1437.1598220000001</v>
+      </c>
+      <c r="Q52">
+        <v>76</v>
+      </c>
+      <c r="S52">
+        <v>76.434211000000005</v>
+      </c>
+      <c r="T52">
+        <v>1.8802570000000001</v>
+      </c>
+      <c r="U52">
+        <v>85</v>
+      </c>
+      <c r="V52">
+        <v>2.102919</v>
+      </c>
+      <c r="W52">
+        <v>68.341176000000004</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>25</v>
+      </c>
+      <c r="B53" t="s">
+        <v>26</v>
+      </c>
+      <c r="C53" t="s">
+        <v>56</v>
+      </c>
+      <c r="D53" t="s">
+        <v>85</v>
+      </c>
+      <c r="E53" t="s">
+        <v>84</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="K53" t="s">
+        <v>34</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53" t="s">
+        <v>83</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>25</v>
+      </c>
+      <c r="B54" t="s">
+        <v>26</v>
+      </c>
+      <c r="C54" t="s">
+        <v>59</v>
+      </c>
+      <c r="D54" t="s">
+        <v>85</v>
+      </c>
+      <c r="E54" t="s">
+        <v>84</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="K54" t="s">
+        <v>34</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54" t="s">
+        <v>83</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="U54">
+        <v>0</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>25</v>
+      </c>
+      <c r="B55" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55" t="s">
+        <v>82</v>
+      </c>
+      <c r="D55" t="s">
+        <v>81</v>
+      </c>
+      <c r="E55" t="s">
+        <v>29</v>
+      </c>
+      <c r="F55">
+        <v>113</v>
+      </c>
+      <c r="G55" t="s">
+        <v>49</v>
+      </c>
+      <c r="H55">
+        <v>2839</v>
+      </c>
+      <c r="I55">
+        <v>1.2007749999999999</v>
+      </c>
+      <c r="J55">
+        <v>54.061946900000002</v>
+      </c>
+      <c r="K55" t="s">
+        <v>34</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>6109</v>
+      </c>
+      <c r="N55" t="s">
+        <v>79</v>
+      </c>
+      <c r="O55">
+        <v>3409</v>
+      </c>
+      <c r="P55">
+        <v>1792.021121</v>
+      </c>
+      <c r="Q55">
+        <v>124</v>
+      </c>
+      <c r="S55">
+        <v>49.266128999999999</v>
+      </c>
+      <c r="T55">
+        <v>3.6374300000000002</v>
+      </c>
+      <c r="U55">
+        <v>145</v>
+      </c>
+      <c r="V55">
+        <v>4.2534470000000004</v>
+      </c>
+      <c r="W55">
+        <v>42.131034</v>
+      </c>
+      <c r="X55">
+        <v>113</v>
+      </c>
+      <c r="Y55">
+        <v>54.061947000000004</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>25</v>
+      </c>
+      <c r="B56" t="s">
+        <v>26</v>
+      </c>
+      <c r="C56" t="s">
+        <v>80</v>
+      </c>
+      <c r="D56" t="s">
+        <v>28</v>
+      </c>
+      <c r="E56" t="s">
+        <v>29</v>
+      </c>
+      <c r="F56">
+        <v>16</v>
+      </c>
+      <c r="G56" t="s">
+        <v>39</v>
+      </c>
+      <c r="H56">
+        <v>322</v>
+      </c>
+      <c r="I56">
+        <v>1.046584</v>
+      </c>
+      <c r="J56">
+        <v>43.875</v>
+      </c>
+      <c r="K56" t="s">
+        <v>34</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>702</v>
+      </c>
+      <c r="N56" t="s">
+        <v>79</v>
+      </c>
+      <c r="O56">
+        <v>337</v>
+      </c>
+      <c r="P56">
+        <v>2083.086053</v>
+      </c>
+      <c r="Q56">
+        <v>16</v>
+      </c>
+      <c r="S56">
+        <v>43.875</v>
+      </c>
+      <c r="T56">
+        <v>4.7477739999999997</v>
+      </c>
+      <c r="U56">
+        <v>18</v>
+      </c>
+      <c r="V56">
+        <v>5.3412459999999999</v>
+      </c>
+      <c r="W56">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>25</v>
+      </c>
+      <c r="B57" t="s">
+        <v>26</v>
+      </c>
+      <c r="C57" t="s">
+        <v>78</v>
+      </c>
+      <c r="D57" t="s">
+        <v>38</v>
+      </c>
+      <c r="E57" t="s">
+        <v>29</v>
+      </c>
+      <c r="F57">
+        <v>43</v>
+      </c>
+      <c r="G57" t="s">
+        <v>49</v>
+      </c>
+      <c r="H57">
+        <v>1925</v>
+      </c>
+      <c r="I57">
+        <v>1.428571</v>
+      </c>
+      <c r="J57">
+        <v>41.534883720000003</v>
+      </c>
+      <c r="K57" t="s">
+        <v>34</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>1786</v>
+      </c>
+      <c r="N57" t="s">
+        <v>76</v>
+      </c>
+      <c r="O57">
+        <v>2750</v>
+      </c>
+      <c r="P57">
+        <v>649.45454500000005</v>
+      </c>
+      <c r="Q57">
+        <v>34</v>
+      </c>
+      <c r="S57">
+        <v>52.529412000000001</v>
+      </c>
+      <c r="T57">
+        <v>1.236364</v>
+      </c>
+      <c r="U57">
+        <v>49</v>
+      </c>
+      <c r="V57">
+        <v>1.7818179999999999</v>
+      </c>
+      <c r="W57">
+        <v>36.448979999999999</v>
+      </c>
+      <c r="X57">
+        <v>43</v>
+      </c>
+      <c r="Y57">
+        <v>41.534883999999998</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>